--- a/GameConfig/Datas/叙事Session配置表.xlsx
+++ b/GameConfig/Datas/叙事Session配置表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,11 @@
           <t>isFormalEnding</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>npcSet</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +514,11 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,6 +566,11 @@
           <t>是否在日终后进入正式结局</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>按剧情配表 Session.NPCSet 的顺序填写 NPC 名，逗号分隔；用于 NPC 对话左右站位</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,6 +618,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -639,6 +659,11 @@
       <c r="I5" t="b">
         <v>0</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>老周,陈先生</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -669,11 +694,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>我能理解钟表的构造，却无法解释老周为何记得这次失约。若我记住了他的遗憾，这算不算也开始理解？</t>
+          <t>2026年10月6日，第24次启动。
+今日检测物品：老式座钟×1
+检测结果：达到【低效物】标准，但物主对其有强烈【情感】寄托，不建议直接按【低效物】处理标准处理，交由物主本人判断。
+钟里……有很多以前的故事，明明隔了那么久，却感觉还是那么鲜活。</t>
         </is>
       </c>
       <c r="I6" t="b">
         <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>老周</t>
+        </is>
       </c>
     </row>
     <row r="7">

--- a/GameConfig/Datas/叙事Session配置表.xlsx
+++ b/GameConfig/Datas/叙事Session配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,8 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -467,6 +470,11 @@
           <t>npcSet</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>backgroundId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +527,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -571,6 +584,11 @@
           <t>按剧情配表 Session.NPCSet 的顺序填写 NPC 名，逗号分隔；用于 NPC 对话左右站位</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>场景背景 ID；为空时回退到按 npcId 选择（旧逻辑）</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -623,6 +641,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -662,6 +685,11 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>老周,陈先生</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>scene_shop_old</t>
         </is>
       </c>
     </row>
@@ -708,6 +736,11 @@
           <t>老周</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>scene_zhou</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -744,6 +777,11 @@
       <c r="I7" t="b">
         <v>0</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>scene_chenguo</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -780,6 +818,11 @@
       <c r="I8" t="b">
         <v>0</v>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>scene_father</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -816,6 +859,11 @@
       <c r="I9" t="b">
         <v>0</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>scene_shop_old</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -852,6 +900,11 @@
       <c r="I10" t="b">
         <v>0</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>scene_zhou</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -888,6 +941,11 @@
       <c r="I11" t="b">
         <v>0</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>scene_shop_old</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -924,6 +982,11 @@
       <c r="I12" t="b">
         <v>0</v>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>scene_shop_old</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -960,6 +1023,11 @@
       <c r="I13" t="b">
         <v>0</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>scene_shop_old</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -990,6 +1058,11 @@
       </c>
       <c r="I14" t="b">
         <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>scene_shop_new</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/叙事Session配置表.xlsx
+++ b/GameConfig/Datas/叙事Session配置表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="叙事Session配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,10 +413,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,6 +484,16 @@
           <t>backgroundId</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>titleDate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>titleLocation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -532,118 +551,148 @@
           <t>string</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Session ID</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Session名称</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>起始节点</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>优先级</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>游戏内天数</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>后续Session</t>
+          <t>c</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>该Session结束后的AI日终独白</t>
+          <t>c</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>是否在日终后进入正式结局</t>
+          <t>c</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>按剧情配表 Session.NPCSet 的顺序填写 NPC 名，逗号分隔；用于 NPC 对话左右站位</t>
+          <t>c</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>场景背景 ID；为空时回退到按 npcId 选择（旧逻辑）</t>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Session ID</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Session名称</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>起始节点</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>优先级</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>游戏内天数</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>后续Session</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>该Session结束后的AI日终独白</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>是否在日终后进入正式结局</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>按剧情配表 Session.NPCSet 的顺序填写 NPC 名，逗号分隔；用于 NPC 对话左右站位</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>场景背景 ID；为空时回退到按 npcId 选择（旧逻辑）</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>开场过场卡日期，如 2026年9月30日；为空则本幕不播过场</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>开场过场卡地点，如 老周修理铺；为空则本幕不播过场</t>
         </is>
       </c>
     </row>
@@ -655,7 +704,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>物有所值</t>
+          <t>平凡世界</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -676,11 +725,16 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>我按维修时间和剩余功能给出结论。可当老周听见那个数字时，像听见一段关系被压扁了。结论仍然正确吗？</t>
-        </is>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
+          <t>2026年9月30日，第21次启动。
+今日检测物品：相机×1，眼镜×1
+检测结果：均达到【低效物】标准，评估后建议丢弃；同时检测到不可量化项目，命名为【情感】。相关数据浓度较高，暂且定性为【干扰项】，具体性质待后续再行判定。
+今日存储记忆中检测到少量【好奇】情感，……什么是好奇？</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -690,6 +744,16 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>scene_shop_old</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026年9月30日</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>老周修理铺</t>
         </is>
       </c>
     </row>
@@ -701,7 +765,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>迟来的钟声</t>
+          <t>导师</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -728,8 +792,10 @@
 钟里……有很多以前的故事，明明隔了那么久，却感觉还是那么鲜活。</t>
         </is>
       </c>
-      <c r="I6" t="b">
-        <v>0</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -739,6 +805,16 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>scene_zhou</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026年10月6日</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>仓库</t>
         </is>
       </c>
     </row>
@@ -750,7 +826,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>布偶的秘密</t>
+          <t>盟友</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -762,24 +838,36 @@
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>我已经能列出布偶的维修项目，也知道重新填充棉花的成本。可陈果抱着它时，手一直护着那道开线。损坏的部分，是她最想留下的部分。</t>
-        </is>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>陈先生,陈果</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>scene_chenguo</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026年10月10日</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>陈果房间</t>
         </is>
       </c>
     </row>
@@ -791,19 +879,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>无法复原</t>
+          <t>盟友·修理铺</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T0401</t>
+          <t>T0326</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -812,15 +900,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>我给出了步骤，陈先生也逐项照做。零件没有因此出现，焊点也没有变得容易。记录里写着“维修失败”，但它不能说明我们什么都没有学会。</t>
-        </is>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
+          <t>2026年10月10日，$PLayerName第（）次启动。
+今日检测物品：布偶【布布】×1
+检测结果：破旧、开线，但陈果很珍惜这只朋友送来的小娃娃。
+我……本来该说，是低效物的，但是……看着果果拿着纸条，想着小满露出笑颜的那一刻……我犹豫了。
+【低效】，真的等同于毫无价值吗？
+【情感】，真的是干扰项吗……？</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>老周,陈果</t>
+        </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>scene_father</t>
+          <t>scene_shop_old</t>
         </is>
       </c>
     </row>
@@ -832,19 +932,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>未完成的约定</t>
+          <t>镜像&amp;试炼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T0501</t>
+          <t>T0401</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -853,15 +953,37 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>一通电话没有让收音机修好，却改变了陈先生看它的方式。我把来电内容归入“新增信息”，但也许真正变化的不是档案，而是他愿不愿意继续听下去。</t>
-        </is>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
+          <t>2026年10月15日，第27次启动。
+今日检测物品：收录机×1
+检测结果：【情感】浓度超标，疑有难忘却承载强烈情绪的记忆被封存在内，但收录机本身严重损坏，磁带仓无法打开，磁带无法取出，磁带内容无从考证。
+收录机坏了，磁带拿不出来，录了什么……
+什么都不知道。什么都忘了。
+有……很奇怪的感觉，这叫……失落吗？</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>陈先生,妻子</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>scene_shop_old</t>
+          <t>scene_father</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026年10月15日</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>父母房间</t>
         </is>
       </c>
     </row>
@@ -873,19 +995,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>以物换物</t>
+          <t>洞穴</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T0601</t>
+          <t>T0501</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -894,15 +1016,37 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>老周拆下自己收音机里的零件时，旧录音也随之失去了播放的可能。他知道代价，仍然动手。我的处置表里没有“愿意承担另一种失去”这一项。</t>
-        </is>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
+          <t>2026年10月16日，第28次启动。
+今日检测物品：无
+老周拆了座钟，拿零件来修陈先生的收音机。
+值得吗？
+……效率层面，不值，但是……
+这个世界上，真的只剩【效率】了吗？</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>老周,陈先生</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>scene_zhou</t>
+          <t>scene_shop_old</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026年10月16日</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>老周修理铺</t>
         </is>
       </c>
     </row>
@@ -914,19 +1058,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>声音归来</t>
+          <t>奖励</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T0701</t>
+          <t>T0601</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -935,15 +1079,38 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>录音里的停顿、称呼和笑声都不是零件，却让一家人重新坐到一起。我仍不能把这种变化换算成维修收益，但我开始希望这段声音能够被听见。</t>
-        </is>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
+          <t>2026年10月22日，$PLayerName第31次启动。
+今日检测物品：磁带×1.
+检测结果：磁带内录音有极强【情感】承载，内容为陈果出生时全家关心的话语。
+原来，她出生时……那么幸福。
+——什么是幸福？
+不知道，但是似乎和【喜悦】很接近吧。
+……感觉，暖暖的。</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>老周,陈先生,陈果</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>scene_shop_old</t>
+          <t>scene_shop_old_fixed</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026年10月22日</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>老周修理铺</t>
         </is>
       </c>
     </row>
@@ -955,19 +1122,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>记忆清单</t>
+          <t>磨难</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T0801</t>
+          <t>T0701</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -976,15 +1143,34 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>清理后，几段记录不再可读取。系统显示容量已恢复，任务已完成。可我面对同一台旧物时，仍然停顿了一下。那一下来自哪里？</t>
-        </is>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
+          <t>2026年10月27日，第36次启动。
+电量耗尽，存储清零，进入休眠状态。
+我……是不是忘记了很多，很重要的东西？</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>陈先生</t>
+        </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>scene_shop_old</t>
+          <t>scene_father</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026年10月27日</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>父母房间</t>
         </is>
       </c>
     </row>
@@ -996,72 +1182,43 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>遗失的回声</t>
+          <t>复活&amp;回归</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>T0901</t>
+          <t>T0801</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>我找不回被删除的原文，却发现自己的选择留下了痕迹。缺失的数据没有回来；改变过我的经历，也没有完全消失。</t>
-        </is>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>老周,陈先生</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>scene_shop_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>成为自己</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>T1001</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" t="n">
-        <v>17</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>我不能完整复述一路上发生过的事，却知道这些人和物已经改变了我的判断。系统要求我给出最优方案。我想先说清楚：这是我的选择。</t>
-        </is>
-      </c>
-      <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
           <t>scene_shop_new</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026年10月30日</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>老周修理铺</t>
         </is>
       </c>
     </row>

--- a/GameConfig/Datas/叙事Session配置表.xlsx
+++ b/GameConfig/Datas/叙事Session配置表.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>scene_zhou</t>
+          <t>scene_warehouse</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">

--- a/GameConfig/Datas/叙事Session配置表.xlsx
+++ b/GameConfig/Datas/叙事Session配置表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -494,6 +494,11 @@
           <t>titleLocation</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>clearMemoriesOnEnd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -561,6 +566,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -628,6 +638,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -693,6 +708,11 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>开场过场卡地点，如 老周修理铺；为空则本幕不播过场</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>该 Session 结束后清空玩家全部记忆（AI 被清退/重启）；情绪、好感、道具保留</t>
         </is>
       </c>
     </row>
@@ -756,6 +776,11 @@
           <t>老周修理铺</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -817,6 +842,11 @@
           <t>仓库</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -868,6 +898,11 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>陈果房间</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -923,6 +958,11 @@
           <t>scene_shop_old</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -986,6 +1026,11 @@
           <t>父母房间</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -1047,6 +1092,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>老周修理铺</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1113,6 +1163,11 @@
           <t>老周修理铺</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1173,6 +1228,11 @@
           <t>父母房间</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -1219,6 +1279,11 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>老周修理铺</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
